--- a/Liste Bewirtung.xlsx
+++ b/Liste Bewirtung.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ff38c7f2fb15de3e/04_Privat/TCM/Website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="46" documentId="8_{2FFFAFA0-CF7F-423B-945C-B77AA0945887}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F2B7582B-0D37-42EC-AE52-03C41F08E3E9}"/>
+  <xr:revisionPtr revIDLastSave="56" documentId="8_{2FFFAFA0-CF7F-423B-945C-B77AA0945887}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6E7DC398-6FD5-4823-A851-5800062760E5}"/>
   <bookViews>
-    <workbookView xWindow="5400" yWindow="1725" windowWidth="21600" windowHeight="11295" xr2:uid="{87B39E5F-0CDE-4DFD-A517-00E6B6C8911A}"/>
+    <workbookView xWindow="-25950" yWindow="2205" windowWidth="21600" windowHeight="11295" xr2:uid="{87B39E5F-0CDE-4DFD-A517-00E6B6C8911A}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="61">
   <si>
     <t>30.4.</t>
   </si>
@@ -195,6 +195,30 @@
   </si>
   <si>
     <t>30.7.</t>
+  </si>
+  <si>
+    <t>Laureen Eberle</t>
+  </si>
+  <si>
+    <t>Valerie J.</t>
+  </si>
+  <si>
+    <t>Leonard K.</t>
+  </si>
+  <si>
+    <t>Patrick H.</t>
+  </si>
+  <si>
+    <t>Jürgen M.</t>
+  </si>
+  <si>
+    <t>Rainer M.</t>
+  </si>
+  <si>
+    <t>Lilith E.</t>
+  </si>
+  <si>
+    <t>Lea S.</t>
   </si>
 </sst>
 </file>
@@ -247,10 +271,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -611,7 +631,7 @@
         <v>38</v>
       </c>
       <c r="B5" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -630,10 +650,10 @@
         <v>36</v>
       </c>
       <c r="B7" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="C7" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -652,10 +672,10 @@
         <v>39</v>
       </c>
       <c r="B9" t="s">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="C9" t="s">
-        <v>35</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -767,10 +787,10 @@
         <v>42</v>
       </c>
       <c r="B20" t="s">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="C20" t="s">
-        <v>35</v>
+        <v>60</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -779,6 +799,9 @@
       </c>
       <c r="B21" t="s">
         <v>33</v>
+      </c>
+      <c r="C21" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">

--- a/Liste Bewirtung.xlsx
+++ b/Liste Bewirtung.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ff38c7f2fb15de3e/04_Privat/TCM/Website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="56" documentId="8_{2FFFAFA0-CF7F-423B-945C-B77AA0945887}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6E7DC398-6FD5-4823-A851-5800062760E5}"/>
+  <xr:revisionPtr revIDLastSave="99" documentId="8_{2FFFAFA0-CF7F-423B-945C-B77AA0945887}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A180B915-08FE-45B6-86AD-95F515DDE6AA}"/>
   <bookViews>
-    <workbookView xWindow="-25950" yWindow="2205" windowWidth="21600" windowHeight="11295" xr2:uid="{87B39E5F-0CDE-4DFD-A517-00E6B6C8911A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{87B39E5F-0CDE-4DFD-A517-00E6B6C8911A}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="73">
   <si>
     <t>30.4.</t>
   </si>
@@ -219,6 +219,42 @@
   </si>
   <si>
     <t>Lea S.</t>
+  </si>
+  <si>
+    <t>Datum</t>
+  </si>
+  <si>
+    <t>Name 1</t>
+  </si>
+  <si>
+    <t>Name 2</t>
+  </si>
+  <si>
+    <t>Event</t>
+  </si>
+  <si>
+    <t>Menu</t>
+  </si>
+  <si>
+    <t>Donnerstags-Bewirtung</t>
+  </si>
+  <si>
+    <t>Bewrtung Damen 1</t>
+  </si>
+  <si>
+    <t>Bewirtung Herren 1</t>
+  </si>
+  <si>
+    <t>Bewirtung Damen 1</t>
+  </si>
+  <si>
+    <t>Bewirtung Herren 1/Damen 1</t>
+  </si>
+  <si>
+    <t>Albert-Weber-Open</t>
+  </si>
+  <si>
+    <t>Wurst/Steak</t>
   </si>
 </sst>
 </file>
@@ -590,10 +626,31 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F917C0E2-B242-48E6-8078-71DEFF5AD22D}">
-  <dimension ref="A2:C32"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="15.42578125" customWidth="1"/>
+    <col min="4" max="4" width="22.42578125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -603,8 +660,11 @@
       <c r="C2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -614,8 +674,11 @@
       <c r="C3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>34</v>
       </c>
@@ -625,16 +688,22 @@
       <c r="C4" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>38</v>
       </c>
       <c r="B5" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -644,8 +713,11 @@
       <c r="C6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D6" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>36</v>
       </c>
@@ -655,8 +727,11 @@
       <c r="C7" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D7" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>37</v>
       </c>
@@ -666,8 +741,11 @@
       <c r="C8" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>39</v>
       </c>
@@ -677,8 +755,11 @@
       <c r="C9" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D9" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>40</v>
       </c>
@@ -688,16 +769,25 @@
       <c r="C10" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D10" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>13</v>
       </c>
       <c r="B11" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D11" t="s">
+        <v>70</v>
+      </c>
+      <c r="E11" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>8</v>
       </c>
@@ -707,8 +797,11 @@
       <c r="C12" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D12" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>41</v>
       </c>
@@ -718,8 +811,11 @@
       <c r="C13" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D13" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>11</v>
       </c>
@@ -729,8 +825,11 @@
       <c r="C14" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D14" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -740,16 +839,25 @@
       <c r="C15" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D15" t="s">
+        <v>68</v>
+      </c>
+      <c r="E15" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>18</v>
       </c>
       <c r="B16" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D16" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>43</v>
       </c>
@@ -759,8 +867,11 @@
       <c r="C17" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D17" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>26</v>
       </c>
@@ -770,8 +881,14 @@
       <c r="C18" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D18" t="s">
+        <v>68</v>
+      </c>
+      <c r="E18" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>29</v>
       </c>
@@ -781,8 +898,14 @@
       <c r="C19" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D19" t="s">
+        <v>68</v>
+      </c>
+      <c r="E19" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>42</v>
       </c>
@@ -792,8 +915,11 @@
       <c r="C20" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D20" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>32</v>
       </c>
@@ -803,8 +929,14 @@
       <c r="C21" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D21" t="s">
+        <v>68</v>
+      </c>
+      <c r="E21" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>52</v>
       </c>
@@ -814,8 +946,11 @@
       <c r="C22" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D22" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>21</v>
       </c>
@@ -825,24 +960,33 @@
       <c r="C23" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D23" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>24</v>
       </c>
       <c r="B24" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D24" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>44</v>
       </c>
       <c r="B25" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D25" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>45</v>
       </c>
@@ -852,8 +996,11 @@
       <c r="C26" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D26" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>46</v>
       </c>
@@ -863,8 +1010,11 @@
       <c r="C27" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D27" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>47</v>
       </c>
@@ -874,8 +1024,11 @@
       <c r="C28" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D28" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>48</v>
       </c>
@@ -885,8 +1038,11 @@
       <c r="C29" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D29" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>49</v>
       </c>
@@ -896,8 +1052,11 @@
       <c r="C30" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D30" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>50</v>
       </c>
@@ -907,8 +1066,11 @@
       <c r="C31" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D31" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>51</v>
       </c>
@@ -917,6 +1079,9 @@
       </c>
       <c r="C32" t="s">
         <v>35</v>
+      </c>
+      <c r="D32" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>
